--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484885_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484885_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.5075</v>
+        <v>6.8577</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4369</v>
+        <v>2.8981</v>
       </c>
       <c r="F2" t="n">
-        <v>5.0707</v>
+        <v>3.9596</v>
       </c>
       <c r="G2" t="n">
         <v>2.3231</v>
@@ -610,13 +610,13 @@
         <v>2.4531</v>
       </c>
       <c r="S2" t="n">
-        <v>4.7504</v>
+        <v>2.1006</v>
       </c>
       <c r="T2" t="n">
-        <v>2.7216</v>
+        <v>1.1828</v>
       </c>
       <c r="U2" t="n">
-        <v>2.0288</v>
+        <v>0.9177</v>
       </c>
       <c r="V2" t="n">
         <v>0.9244</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6447</v>
+        <v>5.0449</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4244</v>
+        <v>4.6394</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2203</v>
+        <v>0.4055</v>
       </c>
       <c r="G3" t="n">
         <v>4.2199</v>
@@ -688,13 +688,13 @@
         <v>1.887</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7266</v>
+        <v>1.1268</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5131</v>
+        <v>0.7281</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2135</v>
+        <v>0.3986</v>
       </c>
       <c r="V3" t="n">
         <v>-1.2452</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5841</v>
+        <v>3.0171</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5195</v>
+        <v>0.7144</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0646</v>
+        <v>2.3027</v>
       </c>
       <c r="G4" t="n">
         <v>2.3857</v>
@@ -766,13 +766,13 @@
         <v>1.5096</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5949</v>
+        <v>1.0279</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1575</v>
+        <v>0.3524</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4374</v>
+        <v>0.6755</v>
       </c>
       <c r="V4" t="n">
         <v>0.9244</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1689</v>
+        <v>1.9173</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0313</v>
+        <v>1.7004</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1375</v>
+        <v>0.2169</v>
       </c>
       <c r="G5" t="n">
         <v>-1.4782</v>
@@ -844,13 +844,13 @@
         <v>1.5096</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6096</v>
+        <v>0.358</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9246</v>
+        <v>0.5937</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3151</v>
+        <v>-0.2357</v>
       </c>
       <c r="V5" t="n">
         <v>2.4714</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. CABRERA GUEDES</t>
+          <t>N. RAMOS CAMPOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5780999999999999</v>
+        <v>0.0733</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5805</v>
+        <v>-1.1152</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0023</v>
+        <v>1.1885</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8448</v>
+        <v>-0.9374</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4375</v>
+        <v>-0.8937</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4073</v>
+        <v>-0.0437</v>
       </c>
       <c r="J8" t="n">
-        <v>2.4543</v>
+        <v>-1.0609</v>
       </c>
       <c r="K8" t="n">
-        <v>2.372</v>
+        <v>-1.1035</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0823</v>
+        <v>0.0426</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6095</v>
+        <v>0.1235</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.9346</v>
+        <v>0.2098</v>
       </c>
       <c r="O8" t="n">
-        <v>0.325</v>
+        <v>-0.0863</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1887</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7548</v>
+        <v>1.5096</v>
       </c>
       <c r="S8" t="n">
-        <v>1.8088</v>
+        <v>0.4447</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.5875</v>
       </c>
       <c r="U8" t="n">
-        <v>1.0976</v>
+        <v>-0.1428</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.8868</v>
+        <v>0.9434</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6415999999999999</v>
+        <v>1.2452</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2452</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. CALATAYUD CERVERA</t>
+          <t>D. CABRERA GUEDES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2302</v>
+        <v>-0.1194</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0999</v>
+        <v>1.3856</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3301</v>
+        <v>-1.505</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0808</v>
+        <v>0.8448</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8241000000000001</v>
+        <v>0.4375</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9049</v>
+        <v>0.4073</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6877</v>
+        <v>2.4543</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0211</v>
+        <v>2.372</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6666</v>
+        <v>0.0823</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6069</v>
+        <v>-1.6095</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8452</v>
+        <v>-1.9346</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2383</v>
+        <v>0.325</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7548</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1887</v>
+        <v>0.7548</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4438</v>
+        <v>1.1113</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3556</v>
+        <v>0.5164</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0882</v>
+        <v>0.595</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.8868</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4318</v>
+        <v>-0.2104</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.07530000000000001</v>
+        <v>0.1196</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3564</v>
+        <v>-0.33</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3318</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0999</v>
+        <v>0.1214</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1176</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0176</v>
+        <v>0.0441</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>N. RAMOS CAMPOS</t>
+          <t>P. CALATAYUD CERVERA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.145</v>
+        <v>-0.2928</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1483</v>
+        <v>-0.095</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0033</v>
+        <v>-0.1978</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9374</v>
+        <v>0.0808</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8937</v>
+        <v>-0.8241000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0437</v>
+        <v>0.9049</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.0609</v>
+        <v>0.6877</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.1035</v>
+        <v>0.0211</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0426</v>
+        <v>0.6666</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1235</v>
+        <v>-0.6069</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2098</v>
+        <v>-0.8452</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0863</v>
+        <v>0.2383</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3774</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5096</v>
+        <v>0.1887</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7736</v>
+        <v>0.3812</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4456</v>
+        <v>0.1608</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.328</v>
+        <v>0.2205</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9434</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.7162</v>
+        <v>-1.4458</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.3404</v>
+        <v>-3.2816</v>
       </c>
       <c r="F12" t="n">
-        <v>1.6242</v>
+        <v>1.8358</v>
       </c>
       <c r="G12" t="n">
         <v>-0.1883</v>
@@ -1390,13 +1390,13 @@
         <v>0.9435</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6607</v>
+        <v>0.9312</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2039</v>
+        <v>0.2627</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4568</v>
+        <v>0.6684</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2452</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>I. CAMBRA DOBRE</t>
+          <t>J. MOLINA LORENZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.5129</v>
+        <v>-1.6981</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.8225</v>
+        <v>-0.1828</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.6904</v>
+        <v>-1.5154</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.8438</v>
+        <v>0.5105</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.8241000000000001</v>
+        <v>0.7638</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.0197</v>
+        <v>-0.2533</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.5873</v>
+        <v>1.2209</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0211</v>
+        <v>1.2365</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.6084000000000001</v>
+        <v>-0.0156</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.2565</v>
+        <v>-0.7104</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.8452</v>
+        <v>-0.4727</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4113</v>
+        <v>-0.2377</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1887</v>
+        <v>-1.5096</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-2.8305</v>
       </c>
       <c r="R13" t="n">
-        <v>0.1887</v>
+        <v>1.3209</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2352</v>
+        <v>0.8669</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2352</v>
+        <v>0.5024</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>0.3645</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.6226</v>
+        <v>-1.566</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.9244</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.6226</v>
+        <v>-2.4904</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. MOLINA LORENZ</t>
+          <t>I. CAMBRA DOBRE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.819</v>
+        <v>-2.318</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.1185</v>
+        <v>-0.6276</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.7006</v>
+        <v>-1.6904</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5105</v>
+        <v>-1.8438</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7638</v>
+        <v>-0.8241000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2533</v>
+        <v>-1.0197</v>
       </c>
       <c r="J14" t="n">
-        <v>1.2209</v>
+        <v>-0.5873</v>
       </c>
       <c r="K14" t="n">
-        <v>1.2365</v>
+        <v>0.0211</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.0156</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7104</v>
+        <v>-1.2565</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4727</v>
+        <v>-0.8452</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2377</v>
+        <v>-0.4113</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.5096</v>
+        <v>0.1887</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.8305</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3209</v>
+        <v>0.1887</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2539</v>
+        <v>-0.0403</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4333</v>
+        <v>-0.0403</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1793</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.566</v>
+        <v>-0.6226</v>
       </c>
       <c r="W14" t="n">
-        <v>0.9244</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.4904</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.1067</v>
+        <v>-2.7162</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.6671</v>
+        <v>-2.647</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4395</v>
+        <v>-0.0692</v>
       </c>
       <c r="G15" t="n">
         <v>-5.0013</v>
@@ -1624,13 +1624,13 @@
         <v>0.9435</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9705</v>
+        <v>1.361</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0545</v>
+        <v>1.0747</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.08400000000000001</v>
+        <v>0.2863</v>
       </c>
       <c r="V15" t="n">
         <v>2.8112</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>9.406300000000002</v>
+        <v>9.994400000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>4.805199999999999</v>
+        <v>5.393099999999997</v>
       </c>
       <c r="F16" t="n">
-        <v>4.601300000000001</v>
+        <v>4.6012</v>
       </c>
       <c r="G16" t="n">
         <v>2.468800000000001</v>
@@ -1681,7 +1681,7 @@
         <v>8.709999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6521000000000002</v>
+        <v>-0.6521000000000003</v>
       </c>
       <c r="M16" t="n">
         <v>-5.5892</v>
@@ -1702,10 +1702,10 @@
         <v>13.209</v>
       </c>
       <c r="S16" t="n">
-        <v>9.2027</v>
+        <v>9.790700000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>5.410300000000001</v>
+        <v>5.998499999999999</v>
       </c>
       <c r="U16" t="n">
         <v>3.7921</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. STANESCU</t>
+          <t>F. ALBERT ABELLAN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.198</v>
+        <v>2.4934</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9303</v>
+        <v>2.2577</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2677</v>
+        <v>0.2357</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5596</v>
+        <v>1.1283</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3195</v>
+        <v>-1.2091</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7599</v>
+        <v>2.3374</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7439</v>
+        <v>2.6849</v>
       </c>
       <c r="K17" t="n">
-        <v>1.3523</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6084000000000001</v>
+        <v>1.8608</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1843</v>
+        <v>-1.5566</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0329</v>
+        <v>-2.0332</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1515</v>
+        <v>0.4765</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3774</v>
+        <v>1.5096</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3774</v>
+        <v>2.4531</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0159</v>
+        <v>-1.1068</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0588</v>
+        <v>-0.7289</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0747</v>
+        <v>-0.3779</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2452</v>
+        <v>0.9624</v>
       </c>
       <c r="W17" t="n">
         <v>1.2452</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2828</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. ALBERT ABELLAN</t>
+          <t>R. STANESCU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.3664</v>
+        <v>2.0129</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5757</v>
+        <v>1.9303</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2093</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>1.1283</v>
+        <v>0.5596</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.2091</v>
+        <v>1.3195</v>
       </c>
       <c r="I18" t="n">
-        <v>2.3374</v>
+        <v>-0.7599</v>
       </c>
       <c r="J18" t="n">
-        <v>2.6849</v>
+        <v>0.7439</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8241000000000001</v>
+        <v>1.3523</v>
       </c>
       <c r="L18" t="n">
-        <v>1.8608</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.5566</v>
+        <v>-0.1843</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.0332</v>
+        <v>-0.0329</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4765</v>
+        <v>-0.1515</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5096</v>
+        <v>0.3774</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.4531</v>
+        <v>0.3774</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.2338</v>
+        <v>-0.1693</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.4109</v>
+        <v>-0.0588</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8229</v>
+        <v>-0.1105</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9624</v>
+        <v>1.2452</v>
       </c>
       <c r="W18" t="n">
         <v>1.2452</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2828</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. BLEDA MIRANDA</t>
+          <t>S. MASSAMBA JOHANSSON</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.3093</v>
+        <v>0.9514</v>
       </c>
       <c r="E19" t="n">
-        <v>2.6517</v>
+        <v>1.2713</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3424</v>
+        <v>-0.3199</v>
       </c>
       <c r="G19" t="n">
-        <v>2.3582</v>
+        <v>-0.3029</v>
       </c>
       <c r="H19" t="n">
-        <v>2.0527</v>
+        <v>-0.2919</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3055</v>
+        <v>-0.011</v>
       </c>
       <c r="J19" t="n">
-        <v>2.4617</v>
+        <v>1.2483</v>
       </c>
       <c r="K19" t="n">
-        <v>1.6802</v>
+        <v>1.1731</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7815</v>
+        <v>0.0752</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1035</v>
+        <v>-1.5512</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3725</v>
+        <v>-1.465</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.476</v>
+        <v>-0.0863</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1322</v>
+        <v>0.9435</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7548</v>
+        <v>1.887</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3285</v>
+        <v>-0.6325</v>
       </c>
       <c r="T19" t="n">
-        <v>1.7752</v>
+        <v>-0.2787</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4467</v>
+        <v>-0.3538</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2452</v>
+        <v>0.9434</v>
       </c>
       <c r="W19" t="n">
-        <v>0.3018</v>
+        <v>1.2452</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.547</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="20">
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. TUDELA GARCIA</t>
+          <t>R. AMOROS PEREZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2872</v>
+        <v>0.0445</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8298</v>
+        <v>-0.1455</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5426</v>
+        <v>0.1899</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6643</v>
+        <v>0.2173</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.4157</v>
+        <v>-0.7050999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7514</v>
+        <v>0.9224</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5780999999999999</v>
+        <v>0.2895</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4547</v>
+        <v>-0.4594</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1234</v>
+        <v>0.7489</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2424</v>
+        <v>-0.0721</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.8704</v>
+        <v>-0.2457</v>
       </c>
       <c r="O21" t="n">
-        <v>0.628</v>
+        <v>0.1736</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.7548</v>
+        <v>1.5096</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.8305</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0757</v>
+        <v>1.5096</v>
       </c>
       <c r="S21" t="n">
-        <v>2.8346</v>
+        <v>-0.894</v>
       </c>
       <c r="T21" t="n">
-        <v>2.7804</v>
+        <v>-0.4349</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0542</v>
+        <v>-0.459</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.1283</v>
+        <v>-0.7885</v>
       </c>
       <c r="W21" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.4301</v>
+        <v>-0.7885</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. MASSAMBA JOHANSSON</t>
+          <t>C. BLEDA MIRANDA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0349</v>
+        <v>-0.1221</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4918</v>
+        <v>1.0928</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5268</v>
+        <v>-1.2148</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3029</v>
+        <v>2.3582</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2919</v>
+        <v>2.0527</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.011</v>
+        <v>0.3055</v>
       </c>
       <c r="J22" t="n">
-        <v>1.2483</v>
+        <v>2.4617</v>
       </c>
       <c r="K22" t="n">
-        <v>1.1731</v>
+        <v>1.6802</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0752</v>
+        <v>0.7815</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.5512</v>
+        <v>-0.1035</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.465</v>
+        <v>0.3725</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0863</v>
+        <v>-0.476</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9435</v>
+        <v>-1.1322</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R22" t="n">
-        <v>1.887</v>
+        <v>0.7548</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6189</v>
+        <v>-0.1029</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0582</v>
+        <v>0.2163</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5607</v>
+        <v>-0.3191</v>
       </c>
       <c r="V22" t="n">
-        <v>0.9434</v>
+        <v>-1.2452</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2452</v>
+        <v>0.3018</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.3018</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2245</v>
+        <v>-0.1715</v>
       </c>
       <c r="E23" t="n">
         <v>0.0669</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2913</v>
+        <v>-0.2384</v>
       </c>
       <c r="G23" t="n">
         <v>-0.3185</v>
@@ -2248,13 +2248,13 @@
         <v>0.3774</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2833</v>
+        <v>-0.2304</v>
       </c>
       <c r="T23" t="n">
         <v>-0.0588</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2246</v>
+        <v>-0.1716</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R. AMOROS PEREZ</t>
+          <t>I. DE ANDREA LUNA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.4459</v>
+        <v>-1.8533</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.8275</v>
+        <v>-0.8977000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6183999999999999</v>
+        <v>-0.9557</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2173</v>
+        <v>-2.2367</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.7050999999999999</v>
+        <v>-1.1262</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9224</v>
+        <v>-1.1105</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2895</v>
+        <v>-1.6508</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.4594</v>
+        <v>-0.4751</v>
       </c>
       <c r="L24" t="n">
-        <v>0.7489</v>
+        <v>-1.1757</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.0721</v>
+        <v>-0.5859</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2457</v>
+        <v>-0.6511</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1736</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>1.5096</v>
+        <v>1.887</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5096</v>
+        <v>1.887</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.3843</v>
+        <v>-1.017</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.117</v>
+        <v>-0.4921</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.2673</v>
+        <v>-0.5249</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.7885</v>
+        <v>-0.4867</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.7885</v>
+        <v>-1.7319</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>I. DE ANDREA LUNA</t>
+          <t>G. TUDELA GARCIA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.6352</v>
+        <v>-1.8732</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.2874</v>
+        <v>-1.5086</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.3478</v>
+        <v>-0.3645</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.2367</v>
+        <v>-0.6643</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.1262</v>
+        <v>-1.4157</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.1105</v>
+        <v>0.7514</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.6508</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.4751</v>
+        <v>0.4547</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.1757</v>
+        <v>0.1234</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.5859</v>
+        <v>-1.2424</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.6511</v>
+        <v>-1.8704</v>
       </c>
       <c r="O25" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.628</v>
       </c>
       <c r="P25" t="n">
-        <v>1.887</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>-2.8305</v>
       </c>
       <c r="R25" t="n">
-        <v>1.887</v>
+        <v>2.0757</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.7988</v>
+        <v>0.6742</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8818</v>
+        <v>0.442</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.917</v>
+        <v>0.2323</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.4867</v>
+        <v>-1.1283</v>
       </c>
       <c r="W25" t="n">
-        <v>1.2452</v>
+        <v>0.3018</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.7319</v>
+        <v>-1.4301</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>J. MUNOZ PALENCIA</t>
+          <t>A. FERRIZ SELLES</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,73 +2437,73 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.8485</v>
+        <v>-2.546</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.6136</v>
+        <v>-3.9013</v>
       </c>
       <c r="F26" t="n">
-        <v>0.765</v>
+        <v>1.3553</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.808</v>
+        <v>-2.2367</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.2293</v>
+        <v>-2.3861</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.5787</v>
+        <v>0.1495</v>
       </c>
       <c r="J26" t="n">
-        <v>-3.1433</v>
+        <v>-1.2266</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.5862000000000001</v>
+        <v>-0.7913</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.5571</v>
+        <v>-0.4354</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3353</v>
+        <v>-1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>0.3569</v>
+        <v>-1.5949</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.0216</v>
+        <v>0.5849</v>
       </c>
       <c r="P26" t="n">
         <v>0.5661</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R26" t="n">
-        <v>0.5661</v>
+        <v>2.4531</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.6067</v>
+        <v>-0.6906</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.4703</v>
+        <v>-0.7876</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1364</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>-0.1849</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>-0.1849</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A. FERRIZ SELLES</t>
+          <t>J. MUNOZ PALENCIA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-3.5866</v>
+        <v>-2.6634</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.5833</v>
+        <v>-3.6136</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9967</v>
+        <v>0.9502</v>
       </c>
       <c r="G27" t="n">
-        <v>-2.2367</v>
+        <v>-2.808</v>
       </c>
       <c r="H27" t="n">
-        <v>-2.3861</v>
+        <v>-0.2293</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1495</v>
+        <v>-2.5787</v>
       </c>
       <c r="J27" t="n">
-        <v>-1.2266</v>
+        <v>-3.1433</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.7913</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.4354</v>
+        <v>-2.5571</v>
       </c>
       <c r="M27" t="n">
-        <v>-1.01</v>
+        <v>0.3353</v>
       </c>
       <c r="N27" t="n">
-        <v>-1.5949</v>
+        <v>0.3569</v>
       </c>
       <c r="O27" t="n">
-        <v>0.5849</v>
+        <v>-0.0216</v>
       </c>
       <c r="P27" t="n">
         <v>0.5661</v>
       </c>
       <c r="Q27" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.4531</v>
+        <v>0.5661</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.7312</v>
+        <v>-0.4215</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.4697</v>
+        <v>-0.4703</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.2615</v>
+        <v>0.0488</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.1849</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>-0.1849</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-4.1087</v>
+        <v>-2.7483</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.1527</v>
+        <v>-1.4706</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.956</v>
+        <v>-1.2777</v>
       </c>
       <c r="G28" t="n">
         <v>1.5181</v>
@@ -2638,13 +2638,13 @@
         <v>2.6418</v>
       </c>
       <c r="S28" t="n">
-        <v>-2.7247</v>
+        <v>-1.3643</v>
       </c>
       <c r="T28" t="n">
-        <v>-1.8224</v>
+        <v>-1.1404</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.9023</v>
+        <v>-0.2239</v>
       </c>
       <c r="V28" t="n">
         <v>-0.8265</v>
@@ -2671,22 +2671,22 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-9.406400000000001</v>
+        <v>-6.1586</v>
       </c>
       <c r="E29" t="n">
         <v>-4.6013</v>
       </c>
       <c r="F29" t="n">
-        <v>-4.805199999999999</v>
+        <v>-1.5573</v>
       </c>
       <c r="G29" t="n">
-        <v>-2.468599999999999</v>
+        <v>-2.4686</v>
       </c>
       <c r="H29" t="n">
         <v>-3.9834</v>
       </c>
       <c r="I29" t="n">
-        <v>1.5148</v>
+        <v>1.514800000000001</v>
       </c>
       <c r="J29" t="n">
         <v>5.589399999999999</v>
@@ -2695,16 +2695,16 @@
         <v>4.7266</v>
       </c>
       <c r="L29" t="n">
-        <v>0.8626</v>
+        <v>0.8625999999999998</v>
       </c>
       <c r="M29" t="n">
-        <v>-8.057799999999999</v>
+        <v>-8.0578</v>
       </c>
       <c r="N29" t="n">
         <v>-8.7102</v>
       </c>
       <c r="O29" t="n">
-        <v>0.6520999999999999</v>
+        <v>0.6521000000000001</v>
       </c>
       <c r="P29" t="n">
         <v>3.774</v>
@@ -2716,13 +2716,13 @@
         <v>16.983</v>
       </c>
       <c r="S29" t="n">
-        <v>-9.2027</v>
+        <v>-5.9551</v>
       </c>
       <c r="T29" t="n">
-        <v>-3.7923</v>
+        <v>-3.7922</v>
       </c>
       <c r="U29" t="n">
-        <v>-5.4105</v>
+        <v>-2.162500000000001</v>
       </c>
       <c r="V29" t="n">
         <v>-1.5091</v>
@@ -2731,7 +2731,7 @@
         <v>6.810600000000001</v>
       </c>
       <c r="X29" t="n">
-        <v>-8.319700000000001</v>
+        <v>-8.319699999999999</v>
       </c>
     </row>
   </sheetData>
